--- a/AAII_Financials/Quarterly/SGMT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SGMT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="92">
   <si>
     <t>SGMT</t>
   </si>
@@ -656,104 +656,108 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44286</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -784,15 +788,15 @@
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
+      <c r="M8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N8" s="3">
+        <v>0</v>
+      </c>
+      <c r="O8" s="3">
         <v>2000</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
@@ -808,14 +812,17 @@
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U8" s="3">
-        <v>0</v>
+      <c r="U8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -876,8 +883,11 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -908,15 +918,15 @@
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M10" s="3">
-        <v>0</v>
+      <c r="M10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N10" s="3">
+        <v>0</v>
+      </c>
+      <c r="O10" s="3">
         <v>2000</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
@@ -938,8 +948,11 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -962,70 +975,74 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E12" s="3">
         <v>7000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>6700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>9700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>7200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>15300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>14200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>12700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>6300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>5300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>5700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>5000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>4700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>4500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>24900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>6400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>5900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>19300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>3400</v>
       </c>
-      <c r="V12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1086,8 +1103,11 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1130,8 +1150,8 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1148,8 +1168,11 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1210,8 +1233,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1231,115 +1257,119 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>15800</v>
+      </c>
+      <c r="E17" s="3">
         <v>11700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>10800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>14300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>11900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>19900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>18200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>16900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>10600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>8800</v>
-      </c>
-      <c r="M17" s="3">
-        <v>9500</v>
       </c>
       <c r="N17" s="3">
         <v>9500</v>
       </c>
       <c r="O17" s="3">
+        <v>9500</v>
+      </c>
+      <c r="P17" s="3">
         <v>7100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>31100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>7200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>8700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>23700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4800</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-15800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-11700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-10800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-14300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-11900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-19900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-18200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-16900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-10600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-8800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-9500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-7500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-7100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-6800</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1349,14 +1379,17 @@
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U18" s="3">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V18" s="3">
         <v>-4800</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1379,8 +1412,9 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1411,20 +1445,20 @@
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
+      <c r="M20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>0</v>
       </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
@@ -1435,59 +1469,62 @@
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U20" s="3">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V20" s="3">
         <v>-700</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-15800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-11700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-10800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-14300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-11900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-19900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-18200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-16900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-10600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-8800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-9500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-7400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-7100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-6800</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1503,8 +1540,11 @@
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1547,8 +1587,8 @@
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -1565,70 +1605,76 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-10700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-9600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-12900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-10400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-18200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-16200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-14600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-8100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-6600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-8200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-6400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-6800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-6600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-30500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-7100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-8700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-24400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-5500</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1671,8 +1717,8 @@
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R24" s="3">
         <v>0</v>
@@ -1689,8 +1735,11 @@
       <c r="V24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1751,132 +1800,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-10700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-9600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-12900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-10400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-18200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-16200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-14600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-8100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-6600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-8200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-6400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-6800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-6600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-30500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-7100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-8700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-24400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-5500</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-10700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-9600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-12900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-10400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-18200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-16200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-14600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-8100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-6600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-8200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-6400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-6800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-6600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-30500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-7100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-8700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-24400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-5500</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1937,8 +1995,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1999,8 +2060,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2061,8 +2125,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2123,8 +2190,11 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2155,20 +2225,20 @@
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
+      <c r="M32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
+      <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>0</v>
       </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
@@ -2179,76 +2249,82 @@
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U32" s="3">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V32" s="3">
         <v>700</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-10700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-9600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-12900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-10400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-18200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-16200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-14600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-8100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-6600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-8200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-6400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-6800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-6600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-30500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-7100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-8700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-24400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-5500</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2309,137 +2385,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-10700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-9600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-12900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-10400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-18200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-16200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-14600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-8100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-6600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-8200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-6400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-6800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-6600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-30500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-7100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-8700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-24400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-5500</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44286</v>
       </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2462,8 +2547,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2486,53 +2572,54 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>165900</v>
+      </c>
+      <c r="E41" s="3">
         <v>36600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>35000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>32500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>42300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>64700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>75800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>77000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>96000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>176800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>75100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>101800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>18500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>12300</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2548,53 +2635,56 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>74200</v>
+      </c>
+      <c r="E42" s="3">
         <v>67900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>78100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>84200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>83100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>79900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>75400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>75500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>70400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>16900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>19800</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
       <c r="O42" s="3">
         <v>0</v>
       </c>
       <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
         <v>12900</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2610,8 +2700,11 @@
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2654,8 +2747,8 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R43" s="3">
         <v>0</v>
@@ -2672,8 +2765,11 @@
       <c r="V43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2716,8 +2812,8 @@
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -2734,53 +2830,56 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>3</v>
+      <c r="D45" s="3">
+        <v>700</v>
       </c>
       <c r="E45" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="F45" s="3">
         <v>500</v>
       </c>
       <c r="G45" s="3">
+        <v>500</v>
+      </c>
+      <c r="H45" s="3">
         <v>800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>400</v>
-      </c>
-      <c r="K45" s="3">
-        <v>100</v>
       </c>
       <c r="L45" s="3">
         <v>100</v>
       </c>
       <c r="M45" s="3">
+        <v>100</v>
+      </c>
+      <c r="N45" s="3">
         <v>400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1400</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2796,53 +2895,56 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>244000</v>
+      </c>
+      <c r="E46" s="3">
         <v>107700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>116400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>119500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>127200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>146100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>152800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>157200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>166800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>194500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>96600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>102800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>21400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>27000</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2858,38 +2960,41 @@
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>3</v>
+      <c r="D47" s="3">
+        <v>17400</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F47" s="3">
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3">
         <v>8800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>10100</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I47" s="3">
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3">
         <v>7400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>17500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>22100</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2920,40 +3025,43 @@
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="E48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3">
         <v>100</v>
       </c>
       <c r="G48" s="3">
+        <v>100</v>
+      </c>
+      <c r="H48" s="3">
         <v>200</v>
       </c>
-      <c r="H48" s="3">
-        <v>0</v>
-      </c>
       <c r="I48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3">
         <v>100</v>
       </c>
       <c r="K48" s="3">
+        <v>100</v>
+      </c>
+      <c r="L48" s="3">
         <v>200</v>
       </c>
-      <c r="L48" s="3">
-        <v>0</v>
-      </c>
       <c r="M48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N48" s="3">
         <v>100</v>
@@ -2962,11 +3070,11 @@
         <v>100</v>
       </c>
       <c r="P48" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q48" s="3">
         <v>200</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2982,8 +3090,11 @@
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3044,8 +3155,11 @@
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3106,8 +3220,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3168,13 +3285,16 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>3</v>
+      <c r="D52" s="3">
+        <v>100</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>3</v>
@@ -3185,12 +3305,12 @@
       <c r="G52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H52" s="3">
+      <c r="H52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I52" s="3">
         <v>100</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3209,8 +3329,8 @@
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P52" s="3">
-        <v>0</v>
+      <c r="P52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q52" s="3">
         <v>0</v>
@@ -3230,8 +3350,11 @@
       <c r="V52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3292,53 +3415,56 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>263400</v>
+      </c>
+      <c r="E54" s="3">
         <v>107800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>116500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>128400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>137400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>146200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>160300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>174800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>189000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>194500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>96700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>102900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>21500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>27300</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3354,8 +3480,11 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3378,8 +3507,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3402,53 +3532,54 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E57" s="3">
         <v>2300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1500</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3464,40 +3595,43 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F58" s="3">
         <v>100</v>
       </c>
       <c r="G58" s="3">
+        <v>100</v>
+      </c>
+      <c r="H58" s="3">
         <v>200</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
       <c r="I58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J58" s="3">
         <v>100</v>
       </c>
       <c r="K58" s="3">
+        <v>100</v>
+      </c>
+      <c r="L58" s="3">
         <v>200</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N58" s="3">
         <v>100</v>
@@ -3509,7 +3643,7 @@
         <v>100</v>
       </c>
       <c r="Q58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R58" s="3">
         <v>0</v>
@@ -3526,13 +3660,16 @@
       <c r="V58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>3</v>
+      <c r="D59" s="3">
+        <v>0</v>
       </c>
       <c r="E59" s="3">
         <v>0</v>
@@ -3544,35 +3681,35 @@
         <v>0</v>
       </c>
       <c r="H59" s="3">
+        <v>0</v>
+      </c>
+      <c r="I59" s="3">
         <v>100</v>
       </c>
-      <c r="I59" s="3">
-        <v>0</v>
-      </c>
       <c r="J59" s="3">
         <v>0</v>
       </c>
       <c r="K59" s="3">
         <v>0</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M59" s="3">
+      <c r="L59" s="3">
+        <v>0</v>
+      </c>
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3">
         <v>600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1000</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3588,52 +3725,55 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E60" s="3">
         <v>5300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>5100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>9100</v>
-      </c>
-      <c r="G60" s="3">
-        <v>7200</v>
       </c>
       <c r="H60" s="3">
         <v>7200</v>
       </c>
       <c r="I60" s="3">
+        <v>7200</v>
+      </c>
+      <c r="J60" s="3">
         <v>4500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5000</v>
-      </c>
-      <c r="O60" s="3">
-        <v>5300</v>
       </c>
       <c r="P60" s="3">
         <v>5300</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
+      <c r="Q60" s="3">
+        <v>5300</v>
       </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
@@ -3650,13 +3790,16 @@
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="E61" s="3">
         <v>0</v>
@@ -3712,8 +3855,11 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3747,11 +3893,11 @@
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N62" s="3">
-        <v>0</v>
-      </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O62" s="3">
+        <v>0</v>
       </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
@@ -3774,8 +3920,11 @@
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3836,8 +3985,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3898,8 +4050,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3960,52 +4115,55 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E66" s="3">
         <v>5300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>9100</v>
-      </c>
-      <c r="G66" s="3">
-        <v>7200</v>
       </c>
       <c r="H66" s="3">
         <v>7200</v>
       </c>
       <c r="I66" s="3">
+        <v>7200</v>
+      </c>
+      <c r="J66" s="3">
         <v>4500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5100</v>
-      </c>
-      <c r="O66" s="3">
-        <v>5300</v>
       </c>
       <c r="P66" s="3">
         <v>5300</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
+      <c r="Q66" s="3">
+        <v>5300</v>
       </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
@@ -4022,8 +4180,11 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4046,8 +4207,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4108,8 +4270,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4170,8 +4335,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4209,13 +4377,13 @@
         <v>0</v>
       </c>
       <c r="O70" s="3">
-        <v>214600</v>
+        <v>0</v>
       </c>
       <c r="P70" s="3">
         <v>214600</v>
       </c>
       <c r="Q70" s="3">
-        <v>0</v>
+        <v>214600</v>
       </c>
       <c r="R70" s="3">
         <v>0</v>
@@ -4232,8 +4400,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4294,53 +4465,56 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-371000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-357000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-346300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-336800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-323900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-313500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-295300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-279100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-264500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-256400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-249700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-241600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-235200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-228500</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4356,8 +4530,11 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4418,8 +4595,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4480,8 +4660,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4542,53 +4725,56 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>256200</v>
+      </c>
+      <c r="E76" s="3">
         <v>102500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>111400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>119300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>130200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>139000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>155800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>170700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>183300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>190000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>91100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>97900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-198400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-192700</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4604,8 +4790,11 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4666,137 +4855,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44286</v>
       </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-10700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-9600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-12900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-10400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-18200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-16200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-14600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-8100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-6600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-8200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-6400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-6800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-6600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-30500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-7100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-8700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-24400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-5500</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4819,8 +5017,9 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4863,8 +5062,8 @@
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R83" s="3">
         <v>0</v>
@@ -4881,8 +5080,11 @@
       <c r="V83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4943,8 +5145,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5005,8 +5210,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5067,8 +5275,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5129,8 +5340,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5191,70 +5405,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-8600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-11800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-10200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-9100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-14500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-11000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-19600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-5600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-6200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-7100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-3900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-5700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-24500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-6100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-4700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-21700</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5277,8 +5497,9 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5321,8 +5542,8 @@
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -5339,8 +5560,11 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5401,8 +5625,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5463,70 +5690,76 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-24000</v>
+      </c>
+      <c r="E94" s="3">
         <v>10200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>14400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-13300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>3400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>9900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-75200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>3000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-19600</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
       <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>12800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>19400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-32000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-41400</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
       <c r="T94" s="3">
         <v>0</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
+      <c r="U94" s="3">
+        <v>0</v>
       </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5549,8 +5782,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5593,8 +5827,8 @@
       <c r="P96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -5611,8 +5845,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5673,8 +5910,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5735,8 +5975,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5797,28 +6040,31 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E100" s="3">
-        <v>0</v>
+      <c r="D100" s="3">
+        <v>164400</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>300</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
+      <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J100" s="3">
         <v>0</v>
@@ -5827,40 +6073,43 @@
         <v>0</v>
       </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>104800</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>87200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-900</v>
-      </c>
-      <c r="P100" s="3">
-        <v>-100</v>
       </c>
       <c r="Q100" s="3">
         <v>-100</v>
       </c>
       <c r="R100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="S100" s="3">
         <v>0</v>
       </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>9700</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5903,8 +6152,8 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -5921,66 +6170,72 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>129300</v>
+      </c>
+      <c r="E102" s="3">
         <v>1600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-9800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-22400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-11100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-18900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-80800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>101600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-26700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>83300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>6200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>12200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-56600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-47600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-4700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-12000</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
